--- a/product_surveys/013_software_features_and_functions_survey--product_surveys.xlsx
+++ b/product_surveys/013_software_features_and_functions_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Features Performance</t>
+          <t>Software Features And Functions Survey Third Page</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Software Features And Functions Survey Fifth Page</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Feature Performance</t>
+          <t>Software Features And Functions Survey Seventh Page</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Software Feature Request</t>
+          <t>Software Features And Functions Survey Ninth Page</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Software Feature Request</t>
+          <t>Software Features And Functions Survey Tenth Page</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Software Feature Request</t>
+          <t>Software Features And Functions Survey Eleventh Page</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Software Feature Request</t>
+          <t>Software Features And Functions Survey Twelfth Page</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Software Feature Request</t>
+          <t>Software Features And Functions Survey Thirteenth Page</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How did you hear about us?</t>
+          <t>Software Features And Functions Survey Fifteenth Page</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How did you hear about us?</t>
+          <t>Software Features And Functions Survey Sixteenth Page</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What would you like to see next?</t>
+          <t>Software Features And Functions Survey Eighteenth Page</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What would you like to see next?</t>
+          <t>Software Features And Functions Survey Nineteenth Page</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How long have you used the software?</t>
+          <t>Software Features And Functions Survey Twenty First Page</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
